--- a/output/yearly_total_coral_cover_iteration_35_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_35_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.259735884462418</v>
+        <v>1.247532760498631</v>
       </c>
       <c r="C3" t="n">
-        <v>4.672929485968059</v>
+        <v>4.709892287032951</v>
       </c>
       <c r="D3" t="n">
-        <v>6.114702768849909</v>
+        <v>6.055444477421572</v>
       </c>
       <c r="E3" t="n">
-        <v>12.04736813928039</v>
+        <v>12.01286952495315</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.390919892691397</v>
+        <v>1.361934792565556</v>
       </c>
       <c r="C4" t="n">
-        <v>5.253307353498503</v>
+        <v>5.367191573152387</v>
       </c>
       <c r="D4" t="n">
-        <v>6.410325604460518</v>
+        <v>6.303600506776622</v>
       </c>
       <c r="E4" t="n">
-        <v>13.05455285065042</v>
+        <v>13.03272687249457</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.574919963892125</v>
+        <v>1.517842230199014</v>
       </c>
       <c r="C5" t="n">
-        <v>6.013430079139865</v>
+        <v>6.229171016640438</v>
       </c>
       <c r="D5" t="n">
-        <v>6.785743052873615</v>
+        <v>6.653572653200096</v>
       </c>
       <c r="E5" t="n">
-        <v>14.3740930959056</v>
+        <v>14.40058590003955</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.775771446967245</v>
+        <v>1.692466923121116</v>
       </c>
       <c r="C6" t="n">
-        <v>6.990683709425287</v>
+        <v>7.267006995688766</v>
       </c>
       <c r="D6" t="n">
-        <v>7.153751542540371</v>
+        <v>6.999893688914874</v>
       </c>
       <c r="E6" t="n">
-        <v>15.9202066989329</v>
+        <v>15.95936760772475</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>1.988684452171383</v>
+        <v>1.883028059381171</v>
       </c>
       <c r="C7" t="n">
-        <v>8.10958850749136</v>
+        <v>8.468667982994429</v>
       </c>
       <c r="D7" t="n">
-        <v>7.544350630553358</v>
+        <v>7.42874960342524</v>
       </c>
       <c r="E7" t="n">
-        <v>17.6426235902161</v>
+        <v>17.78044564580084</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.186574930473421</v>
+        <v>1.122986592894917</v>
       </c>
       <c r="C8" t="n">
-        <v>5.831884165659512</v>
+        <v>6.082967225933431</v>
       </c>
       <c r="D8" t="n">
-        <v>5.83933183147819</v>
+        <v>5.624774215534917</v>
       </c>
       <c r="E8" t="n">
-        <v>12.85779092761112</v>
+        <v>12.83072803436326</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.440093445315412</v>
+        <v>1.384027444539678</v>
       </c>
       <c r="C9" t="n">
-        <v>7.282889479632213</v>
+        <v>7.594528864478533</v>
       </c>
       <c r="D9" t="n">
-        <v>6.364687894376326</v>
+        <v>6.131546111901405</v>
       </c>
       <c r="E9" t="n">
-        <v>15.08767081932395</v>
+        <v>15.11010242091962</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.703941989708423</v>
+        <v>1.661058835605692</v>
       </c>
       <c r="C10" t="n">
-        <v>8.937192383324106</v>
+        <v>9.28837605592917</v>
       </c>
       <c r="D10" t="n">
-        <v>6.900966912832714</v>
+        <v>6.683049239522102</v>
       </c>
       <c r="E10" t="n">
-        <v>17.54210128586524</v>
+        <v>17.63248413105696</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.952205933799985</v>
+        <v>1.916796431611353</v>
       </c>
       <c r="C11" t="n">
-        <v>10.69379253014124</v>
+        <v>11.08359690763853</v>
       </c>
       <c r="D11" t="n">
-        <v>7.382262303466136</v>
+        <v>7.15411609197977</v>
       </c>
       <c r="E11" t="n">
-        <v>20.02826076740736</v>
+        <v>20.15450943122965</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.210302805264202</v>
+        <v>2.163308814205419</v>
       </c>
       <c r="C12" t="n">
-        <v>12.50017712217221</v>
+        <v>12.93753029488054</v>
       </c>
       <c r="D12" t="n">
-        <v>7.94509439250356</v>
+        <v>7.607244428973664</v>
       </c>
       <c r="E12" t="n">
-        <v>22.65557431993997</v>
+        <v>22.70808353805963</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.451521219741149</v>
+        <v>2.390660866750679</v>
       </c>
       <c r="C13" t="n">
-        <v>14.29546811393527</v>
+        <v>14.7951506466041</v>
       </c>
       <c r="D13" t="n">
-        <v>8.362736804863793</v>
+        <v>8.028707154334857</v>
       </c>
       <c r="E13" t="n">
-        <v>25.10972613854021</v>
+        <v>25.21451866768964</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.425379856841859</v>
+        <v>1.367270210227491</v>
       </c>
       <c r="C14" t="n">
-        <v>9.892610194274111</v>
+        <v>10.28893192500151</v>
       </c>
       <c r="D14" t="n">
-        <v>6.328669678317341</v>
+        <v>6.092961872004724</v>
       </c>
       <c r="E14" t="n">
-        <v>17.64665972943331</v>
+        <v>17.74916400723372</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.438927975160465</v>
+        <v>1.373759562552562</v>
       </c>
       <c r="C15" t="n">
-        <v>10.70385777472438</v>
+        <v>11.13896835724656</v>
       </c>
       <c r="D15" t="n">
-        <v>6.333568599361533</v>
+        <v>6.076458693096336</v>
       </c>
       <c r="E15" t="n">
-        <v>18.47635434924638</v>
+        <v>18.58918661289546</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.648639102264626</v>
+        <v>1.576264661507551</v>
       </c>
       <c r="C16" t="n">
-        <v>12.58285415831348</v>
+        <v>13.12258959367725</v>
       </c>
       <c r="D16" t="n">
-        <v>6.774010071917779</v>
+        <v>6.505344995173598</v>
       </c>
       <c r="E16" t="n">
-        <v>21.00550333249588</v>
+        <v>21.2041992503584</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.310692090031747</v>
+        <v>1.256519251711408</v>
       </c>
       <c r="C17" t="n">
-        <v>11.49152377531864</v>
+        <v>11.9881899388971</v>
       </c>
       <c r="D17" t="n">
-        <v>6.283047862500993</v>
+        <v>5.995965198825139</v>
       </c>
       <c r="E17" t="n">
-        <v>19.08526372785138</v>
+        <v>19.24067438943365</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.475586434437041</v>
+        <v>1.418654885067768</v>
       </c>
       <c r="C18" t="n">
-        <v>13.35775743875253</v>
+        <v>13.95929389209863</v>
       </c>
       <c r="D18" t="n">
-        <v>6.68323767918312</v>
+        <v>6.378090857749125</v>
       </c>
       <c r="E18" t="n">
-        <v>21.51658155237269</v>
+        <v>21.75603963491553</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.462470285108304</v>
+        <v>1.407590588440907</v>
       </c>
       <c r="C19" t="n">
-        <v>14.22902907384044</v>
+        <v>14.88062484262609</v>
       </c>
       <c r="D19" t="n">
-        <v>6.754826721776796</v>
+        <v>6.446371410579492</v>
       </c>
       <c r="E19" t="n">
-        <v>22.44632608072554</v>
+        <v>22.73458684164649</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.611440681750715</v>
+        <v>1.545732307905476</v>
       </c>
       <c r="C20" t="n">
-        <v>16.2897175050545</v>
+        <v>16.97077552244459</v>
       </c>
       <c r="D20" t="n">
-        <v>7.145827379947173</v>
+        <v>6.808273066795994</v>
       </c>
       <c r="E20" t="n">
-        <v>25.04698556675238</v>
+        <v>25.32478089714606</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>0.9509011913793757</v>
+        <v>0.9101782966072181</v>
       </c>
       <c r="C21" t="n">
-        <v>11.90234591963776</v>
+        <v>12.35208454295322</v>
       </c>
       <c r="D21" t="n">
-        <v>5.943814760775549</v>
+        <v>5.665263484649602</v>
       </c>
       <c r="E21" t="n">
-        <v>18.79706187179269</v>
+        <v>18.92752632421004</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_total_coral_cover_iteration_35_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_35_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.247532760498631</v>
+        <v>1.258479247400982</v>
       </c>
       <c r="C3" t="n">
-        <v>4.709892287032951</v>
+        <v>4.596186267927086</v>
       </c>
       <c r="D3" t="n">
-        <v>6.055444477421572</v>
+        <v>6.060961899519439</v>
       </c>
       <c r="E3" t="n">
-        <v>12.01286952495315</v>
+        <v>11.91562741484751</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.361934792565556</v>
+        <v>1.391227213692097</v>
       </c>
       <c r="C4" t="n">
-        <v>5.367191573152387</v>
+        <v>5.049752366588144</v>
       </c>
       <c r="D4" t="n">
-        <v>6.303600506776622</v>
+        <v>6.392431004302272</v>
       </c>
       <c r="E4" t="n">
-        <v>13.03272687249457</v>
+        <v>12.83341058458251</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.517842230199014</v>
+        <v>1.567516732561981</v>
       </c>
       <c r="C5" t="n">
-        <v>6.229171016640438</v>
+        <v>5.595868899865613</v>
       </c>
       <c r="D5" t="n">
-        <v>6.653572653200096</v>
+        <v>6.695112575487702</v>
       </c>
       <c r="E5" t="n">
-        <v>14.40058590003955</v>
+        <v>13.85849820791529</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.692466923121116</v>
+        <v>1.766157664412985</v>
       </c>
       <c r="C6" t="n">
-        <v>7.267006995688766</v>
+        <v>6.266044865204448</v>
       </c>
       <c r="D6" t="n">
-        <v>6.999893688914874</v>
+        <v>7.067642001365962</v>
       </c>
       <c r="E6" t="n">
-        <v>15.95936760772475</v>
+        <v>15.0998445309834</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>1.883028059381171</v>
+        <v>1.994877698237156</v>
       </c>
       <c r="C7" t="n">
-        <v>8.468667982994429</v>
+        <v>7.076657928655926</v>
       </c>
       <c r="D7" t="n">
-        <v>7.42874960342524</v>
+        <v>7.491939069041385</v>
       </c>
       <c r="E7" t="n">
-        <v>17.78044564580084</v>
+        <v>16.56347469593447</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.122986592894917</v>
+        <v>1.223352263874429</v>
       </c>
       <c r="C8" t="n">
-        <v>6.082967225933431</v>
+        <v>4.767456285402525</v>
       </c>
       <c r="D8" t="n">
-        <v>5.624774215534917</v>
+        <v>5.712178544644916</v>
       </c>
       <c r="E8" t="n">
-        <v>12.83072803436326</v>
+        <v>11.70298709392187</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.384027444539678</v>
+        <v>1.529425001305809</v>
       </c>
       <c r="C9" t="n">
-        <v>7.594528864478533</v>
+        <v>5.826976864294322</v>
       </c>
       <c r="D9" t="n">
-        <v>6.131546111901405</v>
+        <v>6.241979711269606</v>
       </c>
       <c r="E9" t="n">
-        <v>15.11010242091962</v>
+        <v>13.59838157686974</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.661058835605692</v>
+        <v>1.862198528845938</v>
       </c>
       <c r="C10" t="n">
-        <v>9.28837605592917</v>
+        <v>7.018748214589241</v>
       </c>
       <c r="D10" t="n">
-        <v>6.683049239522102</v>
+        <v>6.771634090950004</v>
       </c>
       <c r="E10" t="n">
-        <v>17.63248413105696</v>
+        <v>15.65258083438518</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.916796431611353</v>
+        <v>2.196516967598899</v>
       </c>
       <c r="C11" t="n">
-        <v>11.08359690763853</v>
+        <v>8.279948131891221</v>
       </c>
       <c r="D11" t="n">
-        <v>7.15411609197977</v>
+        <v>7.295505162572837</v>
       </c>
       <c r="E11" t="n">
-        <v>20.15450943122965</v>
+        <v>17.77197026206296</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.163308814205419</v>
+        <v>2.541260526148486</v>
       </c>
       <c r="C12" t="n">
-        <v>12.93753029488054</v>
+        <v>9.623683963694351</v>
       </c>
       <c r="D12" t="n">
-        <v>7.607244428973664</v>
+        <v>7.807459943663726</v>
       </c>
       <c r="E12" t="n">
-        <v>22.70808353805963</v>
+        <v>19.97240443350656</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.390660866750679</v>
+        <v>2.896826249181001</v>
       </c>
       <c r="C13" t="n">
-        <v>14.7951506466041</v>
+        <v>10.99133493257007</v>
       </c>
       <c r="D13" t="n">
-        <v>8.028707154334857</v>
+        <v>8.35373820006745</v>
       </c>
       <c r="E13" t="n">
-        <v>25.21451866768964</v>
+        <v>22.24189938181852</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.367270210227491</v>
+        <v>1.682597755354523</v>
       </c>
       <c r="C14" t="n">
-        <v>10.28893192500151</v>
+        <v>7.722623791146259</v>
       </c>
       <c r="D14" t="n">
-        <v>6.092961872004724</v>
+        <v>6.346252779700402</v>
       </c>
       <c r="E14" t="n">
-        <v>17.74916400723372</v>
+        <v>15.75147432620119</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.373759562552562</v>
+        <v>1.745085996729833</v>
       </c>
       <c r="C15" t="n">
-        <v>11.13896835724656</v>
+        <v>8.219771011099803</v>
       </c>
       <c r="D15" t="n">
-        <v>6.076458693096336</v>
+        <v>6.381654601915542</v>
       </c>
       <c r="E15" t="n">
-        <v>18.58918661289546</v>
+        <v>16.34651160974518</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.576264661507551</v>
+        <v>2.056457098608751</v>
       </c>
       <c r="C16" t="n">
-        <v>13.12258959367725</v>
+        <v>9.626546748946184</v>
       </c>
       <c r="D16" t="n">
-        <v>6.505344995173598</v>
+        <v>6.871821595691889</v>
       </c>
       <c r="E16" t="n">
-        <v>21.2041992503584</v>
+        <v>18.55482544324683</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.256519251711408</v>
+        <v>1.669992114831994</v>
       </c>
       <c r="C17" t="n">
-        <v>11.9881899388971</v>
+        <v>8.805481691453449</v>
       </c>
       <c r="D17" t="n">
-        <v>5.995965198825139</v>
+        <v>6.406777525667217</v>
       </c>
       <c r="E17" t="n">
-        <v>19.24067438943365</v>
+        <v>16.88225133195266</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.418654885067768</v>
+        <v>1.937322014698401</v>
       </c>
       <c r="C18" t="n">
-        <v>13.95929389209863</v>
+        <v>10.19968124120843</v>
       </c>
       <c r="D18" t="n">
-        <v>6.378090857749125</v>
+        <v>6.874884648529139</v>
       </c>
       <c r="E18" t="n">
-        <v>21.75603963491553</v>
+        <v>19.01188790443597</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.407590588440907</v>
+        <v>1.977092614197439</v>
       </c>
       <c r="C19" t="n">
-        <v>14.88062484262609</v>
+        <v>10.84798815518485</v>
       </c>
       <c r="D19" t="n">
-        <v>6.446371410579492</v>
+        <v>7.009482258781378</v>
       </c>
       <c r="E19" t="n">
-        <v>22.73458684164649</v>
+        <v>19.83456302816367</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.545732307905476</v>
+        <v>2.234349782618274</v>
       </c>
       <c r="C20" t="n">
-        <v>16.97077552244459</v>
+        <v>12.44008840716191</v>
       </c>
       <c r="D20" t="n">
-        <v>6.808273066795994</v>
+        <v>7.501573478058049</v>
       </c>
       <c r="E20" t="n">
-        <v>25.32478089714606</v>
+        <v>22.17601166783823</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>0.9101782966072181</v>
+        <v>1.350040538017959</v>
       </c>
       <c r="C21" t="n">
-        <v>12.35208454295322</v>
+        <v>9.150134040506334</v>
       </c>
       <c r="D21" t="n">
-        <v>5.665263484649602</v>
+        <v>6.270501126840718</v>
       </c>
       <c r="E21" t="n">
-        <v>18.92752632421004</v>
+        <v>16.77067570536501</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_total_coral_cover_iteration_35_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_35_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.258479247400982</v>
+        <v>2.603015202400565</v>
       </c>
       <c r="C3" t="n">
-        <v>4.596186267927086</v>
+        <v>7.688731029752165</v>
       </c>
       <c r="D3" t="n">
-        <v>6.060961899519439</v>
+        <v>8.121044267018164</v>
       </c>
       <c r="E3" t="n">
-        <v>11.91562741484751</v>
+        <v>18.41279049917089</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.391227213692097</v>
+        <v>1.111446009609913</v>
       </c>
       <c r="C4" t="n">
-        <v>5.049752366588144</v>
+        <v>4.422694206408434</v>
       </c>
       <c r="D4" t="n">
-        <v>6.392431004302272</v>
+        <v>5.756488110237021</v>
       </c>
       <c r="E4" t="n">
-        <v>12.83341058458251</v>
+        <v>11.29062832625537</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.567516732561981</v>
+        <v>1.250535328954184</v>
       </c>
       <c r="C5" t="n">
-        <v>5.595868899865613</v>
+        <v>4.954630838710679</v>
       </c>
       <c r="D5" t="n">
-        <v>6.695112575487702</v>
+        <v>6.03399288734101</v>
       </c>
       <c r="E5" t="n">
-        <v>13.85849820791529</v>
+        <v>12.23915905500587</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.766157664412985</v>
+        <v>1.410622405611566</v>
       </c>
       <c r="C6" t="n">
-        <v>6.266044865204448</v>
+        <v>5.622742216949425</v>
       </c>
       <c r="D6" t="n">
-        <v>7.067642001365962</v>
+        <v>6.428662021035142</v>
       </c>
       <c r="E6" t="n">
-        <v>15.0998445309834</v>
+        <v>13.46202664359613</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>1.994877698237156</v>
+        <v>1.572694980625556</v>
       </c>
       <c r="C7" t="n">
-        <v>7.076657928655926</v>
+        <v>6.410464988095094</v>
       </c>
       <c r="D7" t="n">
-        <v>7.491939069041385</v>
+        <v>6.866322042003929</v>
       </c>
       <c r="E7" t="n">
-        <v>16.56347469593447</v>
+        <v>14.84948201072458</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.223352263874429</v>
+        <v>1.743845968445098</v>
       </c>
       <c r="C8" t="n">
-        <v>4.767456285402525</v>
+        <v>7.332939658395611</v>
       </c>
       <c r="D8" t="n">
-        <v>5.712178544644916</v>
+        <v>7.309216439451363</v>
       </c>
       <c r="E8" t="n">
-        <v>11.70298709392187</v>
+        <v>16.38600206629207</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.529425001305809</v>
+        <v>1.910785262555834</v>
       </c>
       <c r="C9" t="n">
-        <v>5.826976864294322</v>
+        <v>8.407207849049499</v>
       </c>
       <c r="D9" t="n">
-        <v>6.241979711269606</v>
+        <v>7.827359409315386</v>
       </c>
       <c r="E9" t="n">
-        <v>13.59838157686974</v>
+        <v>18.14535252092072</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.862198528845938</v>
+        <v>1.169398960436546</v>
       </c>
       <c r="C10" t="n">
-        <v>7.018748214589241</v>
+        <v>6.341334223702126</v>
       </c>
       <c r="D10" t="n">
-        <v>6.771634090950004</v>
+        <v>6.205313079278729</v>
       </c>
       <c r="E10" t="n">
-        <v>15.65258083438518</v>
+        <v>13.7160462634174</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.196516967598899</v>
+        <v>1.113390253909265</v>
       </c>
       <c r="C11" t="n">
-        <v>8.279948131891221</v>
+        <v>6.656210164885204</v>
       </c>
       <c r="D11" t="n">
-        <v>7.295505162572837</v>
+        <v>6.129885403161447</v>
       </c>
       <c r="E11" t="n">
-        <v>17.77197026206296</v>
+        <v>13.89948582195592</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.541260526148486</v>
+        <v>1.210632364014912</v>
       </c>
       <c r="C12" t="n">
-        <v>9.623683963694351</v>
+        <v>7.830498228888899</v>
       </c>
       <c r="D12" t="n">
-        <v>7.807459943663726</v>
+        <v>6.656642133875073</v>
       </c>
       <c r="E12" t="n">
-        <v>19.97240443350656</v>
+        <v>15.69777272677888</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.896826249181001</v>
+        <v>0.9562615338445634</v>
       </c>
       <c r="C13" t="n">
-        <v>10.99133493257007</v>
+        <v>7.449501579824798</v>
       </c>
       <c r="D13" t="n">
-        <v>8.35373820006745</v>
+        <v>6.175605393748221</v>
       </c>
       <c r="E13" t="n">
-        <v>22.24189938181852</v>
+        <v>14.58136850741758</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.682597755354523</v>
+        <v>1.049144684143354</v>
       </c>
       <c r="C14" t="n">
-        <v>7.722623791146259</v>
+        <v>8.714179154958495</v>
       </c>
       <c r="D14" t="n">
-        <v>6.346252779700402</v>
+        <v>6.65137996618031</v>
       </c>
       <c r="E14" t="n">
-        <v>15.75147432620119</v>
+        <v>16.41470380528216</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.745085996729833</v>
+        <v>1.026211057772149</v>
       </c>
       <c r="C15" t="n">
-        <v>8.219771011099803</v>
+        <v>9.396552714272284</v>
       </c>
       <c r="D15" t="n">
-        <v>6.381654601915542</v>
+        <v>6.797140047829834</v>
       </c>
       <c r="E15" t="n">
-        <v>16.34651160974518</v>
+        <v>17.21990381987426</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2.056457098608751</v>
+        <v>1.127979024794373</v>
       </c>
       <c r="C16" t="n">
-        <v>9.626546748946184</v>
+        <v>10.95117965637824</v>
       </c>
       <c r="D16" t="n">
-        <v>6.871821595691889</v>
+        <v>7.413716876005</v>
       </c>
       <c r="E16" t="n">
-        <v>18.55482544324683</v>
+        <v>19.49287555717761</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.669992114831994</v>
+        <v>0.6795952133107696</v>
       </c>
       <c r="C17" t="n">
-        <v>8.805481691453449</v>
+        <v>8.219682653806419</v>
       </c>
       <c r="D17" t="n">
-        <v>6.406777525667217</v>
+        <v>6.264168854148326</v>
       </c>
       <c r="E17" t="n">
-        <v>16.88225133195266</v>
+        <v>15.16344672126552</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.937322014698401</v>
+        <v>0.5331380907912305</v>
       </c>
       <c r="C18" t="n">
-        <v>10.19968124120843</v>
+        <v>7.20377012945182</v>
       </c>
       <c r="D18" t="n">
-        <v>6.874884648529139</v>
+        <v>5.845266926223254</v>
       </c>
       <c r="E18" t="n">
-        <v>19.01188790443597</v>
+        <v>13.58217514646631</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.977092614197439</v>
+        <v>0.6229680057298137</v>
       </c>
       <c r="C19" t="n">
-        <v>10.84798815518485</v>
+        <v>8.856424579826816</v>
       </c>
       <c r="D19" t="n">
-        <v>7.009482258781378</v>
+        <v>6.469648648647184</v>
       </c>
       <c r="E19" t="n">
-        <v>19.83456302816367</v>
+        <v>15.94904123420381</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2.234349782618274</v>
+        <v>0.7078106423308229</v>
       </c>
       <c r="C20" t="n">
-        <v>12.44008840716191</v>
+        <v>10.6067236568662</v>
       </c>
       <c r="D20" t="n">
-        <v>7.501573478058049</v>
+        <v>7.105507001733756</v>
       </c>
       <c r="E20" t="n">
-        <v>22.17601166783823</v>
+        <v>18.42004130093078</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.350040538017959</v>
+        <v>0.7808428540497431</v>
       </c>
       <c r="C21" t="n">
-        <v>9.150134040506334</v>
+        <v>12.3951930846467</v>
       </c>
       <c r="D21" t="n">
-        <v>6.270501126840718</v>
+        <v>7.800633463725711</v>
       </c>
       <c r="E21" t="n">
-        <v>16.77067570536501</v>
+        <v>20.97666940242215</v>
       </c>
     </row>
   </sheetData>
